--- a/Packages/cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Config/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.map/Luban/Config/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3296F4-B3B5-C84C-9569-4B00FC72E9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1B25F4-742F-6246-B4EA-A850234AB305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5020" yWindow="0" windowWidth="38400" windowHeight="20500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Map1" sheetId="1" r:id="rId1"/>
@@ -276,14 +276,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,38 +609,38 @@
         <v>30</v>
       </c>
       <c r="F1" s="4"/>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-      <c r="AI1" s="9"/>
-      <c r="AJ1" s="9"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
     </row>
     <row r="2" spans="1:36">
       <c r="A2" t="s">
@@ -657,38 +657,38 @@
         <v>31</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
     </row>
     <row r="3" spans="1:36">
       <c r="A3" t="s">
@@ -699,38 +699,38 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9"/>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="9"/>
-      <c r="AI3" s="9"/>
-      <c r="AJ3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
     </row>
     <row r="4" spans="1:36">
       <c r="A4" t="s">
@@ -755,54 +755,54 @@
         <v>11</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="10"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L4" s="7"/>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="8"/>
-      <c r="O4" s="10" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="10"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="7"/>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="10"/>
+      <c r="T4" s="8"/>
       <c r="U4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="V4" s="7"/>
-      <c r="W4" s="10" t="s">
+      <c r="W4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="X4" s="10"/>
+      <c r="X4" s="8"/>
       <c r="Y4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="Z4" s="7"/>
-      <c r="AA4" s="10" t="s">
+      <c r="AA4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AB4" s="10"/>
+      <c r="AB4" s="8"/>
       <c r="AC4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="10" t="s">
+      <c r="AE4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AF4" s="10"/>
+      <c r="AF4" s="8"/>
       <c r="AG4" s="7" t="s">
         <v>23</v>
       </c>
@@ -886,7 +886,7 @@
         <v>1009</v>
       </c>
       <c r="Z5" s="3">
-        <v>300003</v>
+        <v>200121</v>
       </c>
       <c r="AA5" s="3">
         <v>10021</v>
@@ -993,7 +993,7 @@
         <v>1009</v>
       </c>
       <c r="Z7" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA7" s="3">
         <v>10021</v>
@@ -1100,7 +1100,7 @@
         <v>1009</v>
       </c>
       <c r="Z8" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA8" s="3">
         <v>10021</v>
@@ -1207,7 +1207,7 @@
         <v>1009</v>
       </c>
       <c r="Z9" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA9" s="3">
         <v>10021</v>
@@ -1314,7 +1314,7 @@
         <v>1009</v>
       </c>
       <c r="Z10" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA10" s="3">
         <v>10021</v>
@@ -1421,7 +1421,7 @@
         <v>1009</v>
       </c>
       <c r="Z11" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA11" s="3">
         <v>10021</v>
@@ -1528,7 +1528,7 @@
         <v>1009</v>
       </c>
       <c r="Z12" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA12" s="3">
         <v>10021</v>
@@ -1635,7 +1635,7 @@
         <v>1009</v>
       </c>
       <c r="Z13" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA13" s="3">
         <v>10021</v>
@@ -1742,7 +1742,7 @@
         <v>1009</v>
       </c>
       <c r="Z14" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA14" s="3">
         <v>10021</v>
@@ -1849,7 +1849,7 @@
         <v>1009</v>
       </c>
       <c r="Z15" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA15" s="3">
         <v>10021</v>
@@ -1956,7 +1956,7 @@
         <v>1009</v>
       </c>
       <c r="Z16" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA16" s="3">
         <v>10021</v>
@@ -2065,11 +2065,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="G1:AJ1"/>
     <mergeCell ref="G2:AJ2"/>
     <mergeCell ref="G3:AJ3"/>
@@ -2083,6 +2078,11 @@
     <mergeCell ref="W4:X4"/>
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2141,38 +2141,38 @@
         <v>30</v>
       </c>
       <c r="F1" s="4"/>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-      <c r="AI1" s="9"/>
-      <c r="AJ1" s="9"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
     </row>
     <row r="2" spans="1:36">
       <c r="A2" t="s">
@@ -2189,38 +2189,38 @@
         <v>31</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
     </row>
     <row r="3" spans="1:36">
       <c r="A3" t="s">
@@ -2231,38 +2231,38 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9"/>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="9"/>
-      <c r="AI3" s="9"/>
-      <c r="AJ3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
     </row>
     <row r="4" spans="1:36">
       <c r="A4" t="s">
@@ -2287,54 +2287,54 @@
         <v>11</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="10"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L4" s="7"/>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="8"/>
-      <c r="O4" s="10" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="10"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="7"/>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="10"/>
+      <c r="T4" s="8"/>
       <c r="U4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="V4" s="7"/>
-      <c r="W4" s="10" t="s">
+      <c r="W4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="X4" s="10"/>
+      <c r="X4" s="8"/>
       <c r="Y4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="Z4" s="7"/>
-      <c r="AA4" s="10" t="s">
+      <c r="AA4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AB4" s="10"/>
+      <c r="AB4" s="8"/>
       <c r="AC4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="10" t="s">
+      <c r="AE4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AF4" s="10"/>
+      <c r="AF4" s="8"/>
       <c r="AG4" s="7" t="s">
         <v>23</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>1009</v>
       </c>
       <c r="Z5" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA5" s="3">
         <v>10021</v>
@@ -2525,7 +2525,7 @@
         <v>1009</v>
       </c>
       <c r="Z6" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA6" s="3">
         <v>10021</v>
@@ -2632,7 +2632,7 @@
         <v>1009</v>
       </c>
       <c r="Z7" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA7" s="3">
         <v>10021</v>
@@ -2739,7 +2739,7 @@
         <v>1009</v>
       </c>
       <c r="Z8" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA8" s="3">
         <v>10021</v>
@@ -2846,7 +2846,7 @@
         <v>1009</v>
       </c>
       <c r="Z9" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA9" s="3">
         <v>10021</v>
@@ -2953,7 +2953,7 @@
         <v>1009</v>
       </c>
       <c r="Z10" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA10" s="3">
         <v>10021</v>
@@ -3060,7 +3060,7 @@
         <v>1009</v>
       </c>
       <c r="Z11" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA11" s="3">
         <v>10021</v>
@@ -3167,7 +3167,7 @@
         <v>1009</v>
       </c>
       <c r="Z12" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA12" s="3">
         <v>10021</v>
@@ -3274,7 +3274,7 @@
         <v>1009</v>
       </c>
       <c r="Z13" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA13" s="3">
         <v>10021</v>
@@ -3381,7 +3381,7 @@
         <v>1009</v>
       </c>
       <c r="Z14" s="3">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="AA14" s="3">
         <v>10021</v>
@@ -3766,6 +3766,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AD4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="G1:AJ1"/>
@@ -3782,8 +3784,6 @@
     <mergeCell ref="AI4:AJ4"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="W4:X4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AB4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Packages/cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.map/Luban/Config/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1B25F4-742F-6246-B4EA-A850234AB305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F51F73E-9DD1-C747-8FB8-B5BFE04E5681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5020" yWindow="0" windowWidth="38400" windowHeight="20500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Map1" sheetId="1" r:id="rId1"/>
@@ -276,14 +276,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,38 +609,38 @@
         <v>30</v>
       </c>
       <c r="F1" s="4"/>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
     </row>
     <row r="2" spans="1:36">
       <c r="A2" t="s">
@@ -657,38 +657,38 @@
         <v>31</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-      <c r="AI2" s="10"/>
-      <c r="AJ2" s="10"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
     </row>
     <row r="3" spans="1:36">
       <c r="A3" t="s">
@@ -699,38 +699,38 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10"/>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
-      <c r="AI3" s="10"/>
-      <c r="AJ3" s="10"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
     </row>
     <row r="4" spans="1:36">
       <c r="A4" t="s">
@@ -755,54 +755,54 @@
         <v>11</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="8"/>
+      <c r="J4" s="10"/>
       <c r="K4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L4" s="7"/>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="8" t="s">
+      <c r="N4" s="8"/>
+      <c r="O4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="8"/>
+      <c r="P4" s="10"/>
       <c r="Q4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="7"/>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="8"/>
+      <c r="T4" s="10"/>
       <c r="U4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="V4" s="7"/>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="X4" s="8"/>
+      <c r="X4" s="10"/>
       <c r="Y4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="Z4" s="7"/>
-      <c r="AA4" s="8" t="s">
+      <c r="AA4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="AB4" s="8"/>
+      <c r="AB4" s="10"/>
       <c r="AC4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="8" t="s">
+      <c r="AE4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AF4" s="8"/>
+      <c r="AF4" s="10"/>
       <c r="AG4" s="7" t="s">
         <v>23</v>
       </c>
@@ -2065,6 +2065,10 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="G1:AJ1"/>
     <mergeCell ref="G2:AJ2"/>
     <mergeCell ref="G3:AJ3"/>
@@ -2079,10 +2083,6 @@
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2141,38 +2141,38 @@
         <v>30</v>
       </c>
       <c r="F1" s="4"/>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
     </row>
     <row r="2" spans="1:36">
       <c r="A2" t="s">
@@ -2189,38 +2189,38 @@
         <v>31</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-      <c r="AI2" s="10"/>
-      <c r="AJ2" s="10"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
     </row>
     <row r="3" spans="1:36">
       <c r="A3" t="s">
@@ -2231,38 +2231,38 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10"/>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
-      <c r="AI3" s="10"/>
-      <c r="AJ3" s="10"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
     </row>
     <row r="4" spans="1:36">
       <c r="A4" t="s">
@@ -2287,54 +2287,54 @@
         <v>11</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="8"/>
+      <c r="J4" s="10"/>
       <c r="K4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L4" s="7"/>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="8" t="s">
+      <c r="N4" s="8"/>
+      <c r="O4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="8"/>
+      <c r="P4" s="10"/>
       <c r="Q4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="7"/>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="8"/>
+      <c r="T4" s="10"/>
       <c r="U4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="V4" s="7"/>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="X4" s="8"/>
+      <c r="X4" s="10"/>
       <c r="Y4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="Z4" s="7"/>
-      <c r="AA4" s="8" t="s">
+      <c r="AA4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="AB4" s="8"/>
+      <c r="AB4" s="10"/>
       <c r="AC4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="8" t="s">
+      <c r="AE4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AF4" s="8"/>
+      <c r="AF4" s="10"/>
       <c r="AG4" s="7" t="s">
         <v>23</v>
       </c>
@@ -3484,8 +3484,12 @@
       <c r="X15" s="5">
         <v>30000</v>
       </c>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
+      <c r="Y15" s="3">
+        <v>1009</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
       <c r="AA15" s="3">
         <v>10021</v>
       </c>
@@ -3587,8 +3591,12 @@
       <c r="X16" s="5">
         <v>30000</v>
       </c>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
+      <c r="Y16" s="3">
+        <v>1009</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0</v>
+      </c>
       <c r="AA16" s="3">
         <v>10021</v>
       </c>
@@ -3694,7 +3702,7 @@
         <v>1009</v>
       </c>
       <c r="Z17" s="3">
-        <v>300003</v>
+        <v>200131</v>
       </c>
       <c r="AA17" s="3">
         <v>10021</v>
@@ -3766,9 +3774,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="G1:AJ1"/>
     <mergeCell ref="G2:AJ2"/>
@@ -3784,6 +3789,9 @@
     <mergeCell ref="AI4:AJ4"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="W4:X4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Packages/cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Map1" sheetId="1" r:id="rId1"/>
     <sheet name="Map2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -42,6 +42,12 @@
     <t>Id</t>
   </si>
   <si>
+    <t>UnitConfigId</t>
+  </si>
+  <si>
+    <t>MapName</t>
+  </si>
+  <si>
     <t>KV</t>
   </si>
   <si>
@@ -51,7 +57,10 @@
     <t>int</t>
   </si>
   <si>
-    <t>map,int,long</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>map,NumericType,long</t>
   </si>
   <si>
     <t>##group</t>
@@ -66,6 +75,9 @@
     <t>名字</t>
   </si>
   <si>
+    <t>所在地图</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -78,6 +90,9 @@
     <t>出生Z坐标</t>
   </si>
   <si>
+    <t>出生面向</t>
+  </si>
+  <si>
     <t>速度Base</t>
   </si>
   <si>
@@ -108,12 +123,42 @@
     <t>MP</t>
   </si>
   <si>
+    <t>Phase</t>
+  </si>
+  <si>
     <t>TrainingDummy</t>
   </si>
   <si>
+    <t>Map1</t>
+  </si>
+  <si>
     <t>训练假人</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>Yaw</t>
+  </si>
+  <si>
+    <t>SpeedBase</t>
+  </si>
+  <si>
+    <t>RadiusBase</t>
+  </si>
+  <si>
+    <t>HeightBase</t>
+  </si>
+  <si>
+    <t>WeightBase</t>
+  </si>
+  <si>
     <t>Boar</t>
   </si>
   <si>
@@ -126,59 +171,24 @@
     <t>熊</t>
   </si>
   <si>
-    <t>MapName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>所在地图</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>出生面向</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Map2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitConfigId</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>NPC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>野猪任务NPC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>野猪任务完成NPC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,13 +210,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -255,34 +258,34 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -594,23 +597,23 @@
     <col min="32" max="36" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -642,23 +645,23 @@
       <c r="AI1" s="9"/>
       <c r="AJ1" s="9"/>
     </row>
-    <row r="2" spans="1:36">
-      <c r="A2" t="s">
-        <v>3</v>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -690,9 +693,9 @@
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
     </row>
-    <row r="3" spans="1:36">
-      <c r="A3" t="s">
-        <v>6</v>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>9</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -700,7 +703,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
@@ -732,87 +735,87 @@
       <c r="AI3" s="9"/>
       <c r="AJ3" s="9"/>
     </row>
-    <row r="4" spans="1:36">
-      <c r="A4" t="s">
-        <v>8</v>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="8" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T4" s="10"/>
       <c r="U4" s="7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V4" s="7"/>
       <c r="W4" s="10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X4" s="10"/>
       <c r="Y4" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Z4" s="7"/>
       <c r="AA4" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AB4" s="10"/>
       <c r="AC4" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AD4" s="7"/>
       <c r="AE4" s="10" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AF4" s="10"/>
       <c r="AG4" s="7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AH4" s="7"/>
       <c r="AI4" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AJ4" s="7"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5">
       <c r="B5" s="3">
         <v>10002</v>
       </c>
@@ -820,106 +823,106 @@
         <v>1002</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1010</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
       </c>
-      <c r="I5" s="3">
-        <v>1011</v>
+      <c r="I5" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J5" s="3">
         <v>25200</v>
       </c>
-      <c r="K5" s="2">
-        <v>1012</v>
+      <c r="K5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L5" s="3">
         <v>-50000</v>
       </c>
-      <c r="M5" s="2">
-        <v>1014</v>
+      <c r="M5" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N5" s="3">
         <v>90</v>
       </c>
-      <c r="O5" s="2">
-        <v>10001</v>
+      <c r="O5" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P5" s="5">
         <v>0</v>
       </c>
-      <c r="Q5" s="3">
-        <v>10051</v>
+      <c r="Q5" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R5" s="5">
         <v>500</v>
       </c>
-      <c r="S5" s="2">
-        <v>10061</v>
+      <c r="S5" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T5" s="5">
         <v>0</v>
       </c>
-      <c r="U5" s="3">
-        <v>10071</v>
+      <c r="U5" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V5" s="5">
         <v>500</v>
       </c>
-      <c r="W5" s="3">
-        <v>10081</v>
+      <c r="W5" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X5" s="5">
         <v>30000</v>
       </c>
-      <c r="Y5" s="3">
-        <v>1009</v>
+      <c r="Y5" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z5" s="3">
         <v>200121</v>
       </c>
-      <c r="AA5" s="3">
-        <v>10021</v>
+      <c r="AA5" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB5" s="5">
         <v>100</v>
       </c>
-      <c r="AC5" s="3">
-        <v>1001</v>
+      <c r="AC5" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD5" s="5">
         <v>100</v>
       </c>
-      <c r="AE5" s="3">
-        <v>10041</v>
+      <c r="AE5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF5" s="5">
         <v>100</v>
       </c>
-      <c r="AG5" s="3">
-        <v>1003</v>
+      <c r="AG5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH5" s="5">
         <v>100</v>
       </c>
-      <c r="AI5" s="3">
-        <v>1015</v>
+      <c r="AI5" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ5" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7">
       <c r="B7" s="3">
         <v>10004</v>
       </c>
@@ -927,106 +930,106 @@
         <v>1003</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1010</v>
       </c>
       <c r="H7" s="5">
         <v>21600</v>
       </c>
-      <c r="I7" s="3">
-        <v>1011</v>
+      <c r="I7" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J7" s="5">
         <v>26800</v>
       </c>
-      <c r="K7" s="2">
-        <v>1012</v>
+      <c r="K7" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L7" s="5">
         <v>-58702</v>
       </c>
-      <c r="M7" s="2">
-        <v>1014</v>
+      <c r="M7" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N7" s="3">
         <v>0</v>
       </c>
-      <c r="O7" s="2">
-        <v>10001</v>
+      <c r="O7" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P7" s="5">
         <v>2000</v>
       </c>
-      <c r="Q7" s="3">
-        <v>10051</v>
+      <c r="Q7" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R7" s="5">
         <v>500</v>
       </c>
-      <c r="S7" s="2">
-        <v>10061</v>
+      <c r="S7" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T7" s="5">
         <v>10000</v>
       </c>
-      <c r="U7" s="3">
-        <v>10071</v>
+      <c r="U7" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V7" s="5">
         <v>500</v>
       </c>
-      <c r="W7" s="3">
-        <v>10081</v>
+      <c r="W7" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X7" s="5">
         <v>30000</v>
       </c>
-      <c r="Y7" s="3">
-        <v>1009</v>
+      <c r="Y7" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z7" s="3">
         <v>300001</v>
       </c>
-      <c r="AA7" s="3">
-        <v>10021</v>
+      <c r="AA7" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB7" s="5">
         <v>100</v>
       </c>
-      <c r="AC7" s="3">
-        <v>1001</v>
+      <c r="AC7" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD7" s="5">
         <v>100</v>
       </c>
-      <c r="AE7" s="3">
-        <v>10041</v>
+      <c r="AE7" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF7" s="5">
         <v>100</v>
       </c>
-      <c r="AG7" s="3">
-        <v>1003</v>
+      <c r="AG7" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH7" s="5">
         <v>100</v>
       </c>
-      <c r="AI7" s="3">
-        <v>1015</v>
+      <c r="AI7" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ7" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8">
       <c r="B8" s="3">
         <v>10005</v>
       </c>
@@ -1034,106 +1037,106 @@
         <v>1003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1010</v>
       </c>
       <c r="H8" s="5">
         <v>56000</v>
       </c>
-      <c r="I8" s="3">
-        <v>1011</v>
+      <c r="I8" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J8" s="5">
         <v>25180</v>
       </c>
-      <c r="K8" s="2">
-        <v>1012</v>
+      <c r="K8" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L8" s="5">
         <v>-23633</v>
       </c>
-      <c r="M8" s="2">
-        <v>1014</v>
+      <c r="M8" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
-      <c r="O8" s="2">
-        <v>10001</v>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P8" s="5">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
-        <v>10051</v>
+      <c r="Q8" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R8" s="5">
         <v>500</v>
       </c>
-      <c r="S8" s="2">
-        <v>10061</v>
+      <c r="S8" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T8" s="5">
         <v>10000</v>
       </c>
-      <c r="U8" s="3">
-        <v>10071</v>
+      <c r="U8" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V8" s="5">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
-        <v>10081</v>
+      <c r="W8" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X8" s="5">
         <v>30000</v>
       </c>
-      <c r="Y8" s="3">
-        <v>1009</v>
+      <c r="Y8" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z8" s="3">
         <v>300001</v>
       </c>
-      <c r="AA8" s="3">
-        <v>10021</v>
+      <c r="AA8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB8" s="5">
         <v>100</v>
       </c>
-      <c r="AC8" s="3">
-        <v>1001</v>
+      <c r="AC8" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD8" s="5">
         <v>100</v>
       </c>
-      <c r="AE8" s="3">
-        <v>10041</v>
+      <c r="AE8" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF8" s="5">
         <v>100</v>
       </c>
-      <c r="AG8" s="3">
-        <v>1003</v>
+      <c r="AG8" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH8" s="5">
         <v>100</v>
       </c>
-      <c r="AI8" s="3">
-        <v>1015</v>
+      <c r="AI8" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ8" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9">
       <c r="B9" s="3">
         <v>10006</v>
       </c>
@@ -1141,106 +1144,106 @@
         <v>1003</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1010</v>
       </c>
       <c r="H9" s="5">
         <v>36310</v>
       </c>
-      <c r="I9" s="3">
-        <v>1011</v>
+      <c r="I9" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J9" s="5">
         <v>25180</v>
       </c>
-      <c r="K9" s="2">
-        <v>1012</v>
+      <c r="K9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L9" s="5">
         <v>-23634</v>
       </c>
-      <c r="M9" s="2">
-        <v>1014</v>
+      <c r="M9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="2">
-        <v>10001</v>
+      <c r="O9" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P9" s="5">
         <v>2000</v>
       </c>
-      <c r="Q9" s="3">
-        <v>10051</v>
+      <c r="Q9" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R9" s="5">
         <v>500</v>
       </c>
-      <c r="S9" s="2">
-        <v>10061</v>
+      <c r="S9" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T9" s="5">
         <v>10000</v>
       </c>
-      <c r="U9" s="3">
-        <v>10071</v>
+      <c r="U9" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V9" s="5">
         <v>500</v>
       </c>
-      <c r="W9" s="3">
-        <v>10081</v>
+      <c r="W9" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X9" s="5">
         <v>30000</v>
       </c>
-      <c r="Y9" s="3">
-        <v>1009</v>
+      <c r="Y9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z9" s="3">
         <v>300001</v>
       </c>
-      <c r="AA9" s="3">
-        <v>10021</v>
+      <c r="AA9" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB9" s="5">
         <v>100</v>
       </c>
-      <c r="AC9" s="3">
-        <v>1001</v>
+      <c r="AC9" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD9" s="5">
         <v>100</v>
       </c>
-      <c r="AE9" s="3">
-        <v>10041</v>
+      <c r="AE9" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF9" s="5">
         <v>100</v>
       </c>
-      <c r="AG9" s="3">
-        <v>1003</v>
+      <c r="AG9" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH9" s="5">
         <v>100</v>
       </c>
-      <c r="AI9" s="3">
-        <v>1015</v>
+      <c r="AI9" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ9" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10">
       <c r="B10" s="3">
         <v>10007</v>
       </c>
@@ -1248,106 +1251,106 @@
         <v>1003</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1010</v>
       </c>
       <c r="H10" s="5">
         <v>67170</v>
       </c>
-      <c r="I10" s="3">
-        <v>1011</v>
+      <c r="I10" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J10" s="5">
         <v>25180</v>
       </c>
-      <c r="K10" s="2">
-        <v>1012</v>
+      <c r="K10" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L10" s="5">
         <v>-40495</v>
       </c>
-      <c r="M10" s="2">
-        <v>1014</v>
+      <c r="M10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="2">
-        <v>10001</v>
+      <c r="O10" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P10" s="5">
         <v>2000</v>
       </c>
-      <c r="Q10" s="3">
-        <v>10051</v>
+      <c r="Q10" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R10" s="5">
         <v>500</v>
       </c>
-      <c r="S10" s="2">
-        <v>10061</v>
+      <c r="S10" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T10" s="5">
         <v>10000</v>
       </c>
-      <c r="U10" s="3">
-        <v>10071</v>
+      <c r="U10" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V10" s="5">
         <v>500</v>
       </c>
-      <c r="W10" s="3">
-        <v>10081</v>
+      <c r="W10" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X10" s="5">
         <v>30000</v>
       </c>
-      <c r="Y10" s="3">
-        <v>1009</v>
+      <c r="Y10" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z10" s="3">
         <v>300001</v>
       </c>
-      <c r="AA10" s="3">
-        <v>10021</v>
+      <c r="AA10" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB10" s="5">
         <v>100</v>
       </c>
-      <c r="AC10" s="3">
-        <v>1001</v>
+      <c r="AC10" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD10" s="5">
         <v>100</v>
       </c>
-      <c r="AE10" s="3">
-        <v>10041</v>
+      <c r="AE10" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF10" s="5">
         <v>100</v>
       </c>
-      <c r="AG10" s="3">
-        <v>1003</v>
+      <c r="AG10" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH10" s="5">
         <v>100</v>
       </c>
-      <c r="AI10" s="3">
-        <v>1015</v>
+      <c r="AI10" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ10" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11">
       <c r="B11" s="3">
         <v>10008</v>
       </c>
@@ -1355,106 +1358,106 @@
         <v>1003</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1010</v>
       </c>
       <c r="H11" s="5">
         <v>59600</v>
       </c>
-      <c r="I11" s="3">
-        <v>1011</v>
+      <c r="I11" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J11" s="5">
         <v>25800</v>
       </c>
-      <c r="K11" s="2">
-        <v>1012</v>
+      <c r="K11" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L11" s="5">
         <v>-87866</v>
       </c>
-      <c r="M11" s="2">
-        <v>1014</v>
+      <c r="M11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N11" s="3">
         <v>0</v>
       </c>
-      <c r="O11" s="2">
-        <v>10001</v>
+      <c r="O11" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P11" s="5">
         <v>2000</v>
       </c>
-      <c r="Q11" s="3">
-        <v>10051</v>
+      <c r="Q11" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R11" s="5">
         <v>500</v>
       </c>
-      <c r="S11" s="2">
-        <v>10061</v>
+      <c r="S11" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T11" s="5">
         <v>10000</v>
       </c>
-      <c r="U11" s="3">
-        <v>10071</v>
+      <c r="U11" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V11" s="5">
         <v>500</v>
       </c>
-      <c r="W11" s="3">
-        <v>10081</v>
+      <c r="W11" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X11" s="5">
         <v>30000</v>
       </c>
-      <c r="Y11" s="3">
-        <v>1009</v>
+      <c r="Y11" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z11" s="3">
         <v>300001</v>
       </c>
-      <c r="AA11" s="3">
-        <v>10021</v>
+      <c r="AA11" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB11" s="5">
         <v>100</v>
       </c>
-      <c r="AC11" s="3">
-        <v>1001</v>
+      <c r="AC11" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD11" s="5">
         <v>100</v>
       </c>
-      <c r="AE11" s="3">
-        <v>10041</v>
+      <c r="AE11" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF11" s="5">
         <v>100</v>
       </c>
-      <c r="AG11" s="3">
-        <v>1003</v>
+      <c r="AG11" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH11" s="5">
         <v>100</v>
       </c>
-      <c r="AI11" s="3">
-        <v>1015</v>
+      <c r="AI11" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12">
       <c r="B12" s="3">
         <v>10009</v>
       </c>
@@ -1462,106 +1465,106 @@
         <v>1004</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1010</v>
       </c>
       <c r="H12" s="5">
         <v>58740</v>
       </c>
-      <c r="I12" s="3">
-        <v>1011</v>
+      <c r="I12" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J12" s="5">
         <v>28100</v>
       </c>
-      <c r="K12" s="2">
-        <v>1012</v>
+      <c r="K12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L12" s="5">
         <v>-141407</v>
       </c>
-      <c r="M12" s="2">
-        <v>1014</v>
+      <c r="M12" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N12" s="3">
         <v>0</v>
       </c>
-      <c r="O12" s="2">
-        <v>10001</v>
+      <c r="O12" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P12" s="5">
         <v>2000</v>
       </c>
-      <c r="Q12" s="3">
-        <v>10051</v>
+      <c r="Q12" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R12" s="5">
         <v>2000</v>
       </c>
-      <c r="S12" s="2">
-        <v>10061</v>
+      <c r="S12" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T12" s="5">
         <v>10000</v>
       </c>
-      <c r="U12" s="3">
-        <v>10071</v>
+      <c r="U12" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V12" s="5">
         <v>500</v>
       </c>
-      <c r="W12" s="3">
-        <v>10081</v>
+      <c r="W12" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X12" s="5">
         <v>30000</v>
       </c>
-      <c r="Y12" s="3">
-        <v>1009</v>
+      <c r="Y12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z12" s="3">
         <v>300001</v>
       </c>
-      <c r="AA12" s="3">
-        <v>10021</v>
+      <c r="AA12" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB12" s="5">
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
-        <v>1001</v>
+      <c r="AC12" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD12" s="5">
         <v>100</v>
       </c>
-      <c r="AE12" s="3">
-        <v>10041</v>
+      <c r="AE12" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF12" s="5">
         <v>100</v>
       </c>
-      <c r="AG12" s="3">
-        <v>1003</v>
+      <c r="AG12" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH12" s="5">
         <v>100</v>
       </c>
-      <c r="AI12" s="3">
-        <v>1015</v>
+      <c r="AI12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ12" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13">
       <c r="B13" s="3">
         <v>10010</v>
       </c>
@@ -1569,106 +1572,106 @@
         <v>1004</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1010</v>
       </c>
       <c r="H13" s="5">
         <v>58740</v>
       </c>
-      <c r="I13" s="3">
-        <v>1011</v>
+      <c r="I13" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J13" s="5">
         <v>28100</v>
       </c>
-      <c r="K13" s="2">
-        <v>1012</v>
+      <c r="K13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L13" s="5">
         <v>-130408</v>
       </c>
-      <c r="M13" s="2">
-        <v>1014</v>
+      <c r="M13" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="2">
-        <v>10001</v>
+      <c r="O13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P13" s="5">
         <v>2000</v>
       </c>
-      <c r="Q13" s="3">
-        <v>10051</v>
+      <c r="Q13" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R13" s="5">
         <v>2000</v>
       </c>
-      <c r="S13" s="2">
-        <v>10061</v>
+      <c r="S13" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T13" s="5">
         <v>10000</v>
       </c>
-      <c r="U13" s="3">
-        <v>10071</v>
+      <c r="U13" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V13" s="5">
         <v>500</v>
       </c>
-      <c r="W13" s="3">
-        <v>10081</v>
+      <c r="W13" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X13" s="5">
         <v>30000</v>
       </c>
-      <c r="Y13" s="3">
-        <v>1009</v>
+      <c r="Y13" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z13" s="3">
         <v>300001</v>
       </c>
-      <c r="AA13" s="3">
-        <v>10021</v>
+      <c r="AA13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB13" s="5">
         <v>100</v>
       </c>
-      <c r="AC13" s="3">
-        <v>1001</v>
+      <c r="AC13" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD13" s="5">
         <v>100</v>
       </c>
-      <c r="AE13" s="3">
-        <v>10041</v>
+      <c r="AE13" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF13" s="5">
         <v>100</v>
       </c>
-      <c r="AG13" s="3">
-        <v>1003</v>
+      <c r="AG13" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH13" s="5">
         <v>100</v>
       </c>
-      <c r="AI13" s="3">
-        <v>1015</v>
+      <c r="AI13" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ13" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14">
       <c r="B14" s="3">
         <v>10011</v>
       </c>
@@ -1676,106 +1679,106 @@
         <v>1004</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1010</v>
       </c>
       <c r="H14" s="5">
         <v>67480</v>
       </c>
-      <c r="I14" s="3">
-        <v>1011</v>
+      <c r="I14" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J14" s="5">
         <v>28850</v>
       </c>
-      <c r="K14" s="2">
-        <v>1012</v>
+      <c r="K14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L14" s="5">
         <v>-130409</v>
       </c>
-      <c r="M14" s="2">
-        <v>1014</v>
+      <c r="M14" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="2">
-        <v>10001</v>
+      <c r="O14" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P14" s="5">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>10051</v>
+      <c r="Q14" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R14" s="5">
         <v>2000</v>
       </c>
-      <c r="S14" s="2">
-        <v>10061</v>
+      <c r="S14" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T14" s="5">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
-        <v>10071</v>
+      <c r="U14" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V14" s="5">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
-        <v>10081</v>
+      <c r="W14" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X14" s="5">
         <v>30000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>1009</v>
+      <c r="Y14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z14" s="3">
         <v>300001</v>
       </c>
-      <c r="AA14" s="3">
-        <v>10021</v>
+      <c r="AA14" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB14" s="5">
         <v>100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>1001</v>
+      <c r="AC14" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD14" s="5">
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>10041</v>
+      <c r="AE14" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF14" s="5">
         <v>100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>1003</v>
+      <c r="AG14" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH14" s="5">
         <v>100</v>
       </c>
-      <c r="AI14" s="3">
-        <v>1015</v>
+      <c r="AI14" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ14" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15">
       <c r="B15" s="3">
         <v>10012</v>
       </c>
@@ -1783,106 +1786,106 @@
         <v>1004</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1010</v>
       </c>
       <c r="H15" s="5">
         <v>67480</v>
       </c>
-      <c r="I15" s="3">
-        <v>1011</v>
+      <c r="I15" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J15" s="5">
         <v>27510</v>
       </c>
-      <c r="K15" s="2">
-        <v>1012</v>
+      <c r="K15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L15" s="5">
         <v>-34791</v>
       </c>
-      <c r="M15" s="2">
-        <v>1014</v>
+      <c r="M15" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="2">
-        <v>10001</v>
+      <c r="O15" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P15" s="5">
         <v>2000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>10051</v>
+      <c r="Q15" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R15" s="5">
         <v>2000</v>
       </c>
-      <c r="S15" s="2">
-        <v>10061</v>
+      <c r="S15" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T15" s="5">
         <v>10000</v>
       </c>
-      <c r="U15" s="3">
-        <v>10071</v>
+      <c r="U15" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V15" s="5">
         <v>500</v>
       </c>
-      <c r="W15" s="3">
-        <v>10081</v>
+      <c r="W15" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X15" s="5">
         <v>30000</v>
       </c>
-      <c r="Y15" s="3">
-        <v>1009</v>
+      <c r="Y15" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z15" s="3">
         <v>300001</v>
       </c>
-      <c r="AA15" s="3">
-        <v>10021</v>
+      <c r="AA15" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB15" s="5">
         <v>100</v>
       </c>
-      <c r="AC15" s="3">
-        <v>1001</v>
+      <c r="AC15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD15" s="5">
         <v>100</v>
       </c>
-      <c r="AE15" s="3">
-        <v>10041</v>
+      <c r="AE15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF15" s="5">
         <v>100</v>
       </c>
-      <c r="AG15" s="3">
-        <v>1003</v>
+      <c r="AG15" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH15" s="5">
         <v>100</v>
       </c>
-      <c r="AI15" s="3">
-        <v>1015</v>
+      <c r="AI15" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ15" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16">
       <c r="B16" s="3">
         <v>10013</v>
       </c>
@@ -1890,106 +1893,106 @@
         <v>1004</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="3">
-        <v>1010</v>
       </c>
       <c r="H16" s="5">
         <v>67480</v>
       </c>
-      <c r="I16" s="3">
-        <v>1011</v>
+      <c r="I16" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J16" s="5">
         <v>25900</v>
       </c>
-      <c r="K16" s="2">
-        <v>1012</v>
+      <c r="K16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L16" s="5">
         <v>-93811</v>
       </c>
-      <c r="M16" s="2">
-        <v>1014</v>
+      <c r="M16" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N16" s="3">
         <v>0</v>
       </c>
-      <c r="O16" s="2">
-        <v>10001</v>
+      <c r="O16" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P16" s="5">
         <v>2000</v>
       </c>
-      <c r="Q16" s="3">
-        <v>10051</v>
+      <c r="Q16" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R16" s="5">
         <v>2000</v>
       </c>
-      <c r="S16" s="2">
-        <v>10061</v>
+      <c r="S16" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T16" s="5">
         <v>10000</v>
       </c>
-      <c r="U16" s="3">
-        <v>10071</v>
+      <c r="U16" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V16" s="5">
         <v>500</v>
       </c>
-      <c r="W16" s="3">
-        <v>10081</v>
+      <c r="W16" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X16" s="5">
         <v>30000</v>
       </c>
-      <c r="Y16" s="3">
-        <v>1009</v>
+      <c r="Y16" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z16" s="3">
         <v>300001</v>
       </c>
-      <c r="AA16" s="3">
-        <v>10021</v>
+      <c r="AA16" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB16" s="5">
         <v>100</v>
       </c>
-      <c r="AC16" s="3">
-        <v>1001</v>
+      <c r="AC16" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD16" s="5">
         <v>100</v>
       </c>
-      <c r="AE16" s="3">
-        <v>10041</v>
+      <c r="AE16" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF16" s="5">
         <v>100</v>
       </c>
-      <c r="AG16" s="3">
-        <v>1003</v>
+      <c r="AG16" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH16" s="5">
         <v>100</v>
       </c>
-      <c r="AI16" s="3">
-        <v>1015</v>
+      <c r="AI16" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ16" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:36">
+    <row r="17">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -2026,7 +2029,7 @@
       <c r="AI17" s="6"/>
       <c r="AJ17" s="6"/>
     </row>
-    <row r="18" spans="2:36">
+    <row r="18">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -2064,7 +2067,7 @@
       <c r="AJ18" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AG4:AH4"/>
     <mergeCell ref="AI4:AJ4"/>
@@ -2087,6 +2090,7 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2126,23 +2130,23 @@
     <col min="32" max="36" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -2174,23 +2178,23 @@
       <c r="AI1" s="9"/>
       <c r="AJ1" s="9"/>
     </row>
-    <row r="2" spans="1:36">
-      <c r="A2" t="s">
-        <v>3</v>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -2222,9 +2226,9 @@
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
     </row>
-    <row r="3" spans="1:36">
-      <c r="A3" t="s">
-        <v>6</v>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>9</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2232,7 +2236,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
@@ -2264,87 +2268,87 @@
       <c r="AI3" s="9"/>
       <c r="AJ3" s="9"/>
     </row>
-    <row r="4" spans="1:36">
-      <c r="A4" t="s">
-        <v>8</v>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="8" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T4" s="10"/>
       <c r="U4" s="7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V4" s="7"/>
       <c r="W4" s="10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X4" s="10"/>
       <c r="Y4" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Z4" s="7"/>
       <c r="AA4" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AB4" s="10"/>
       <c r="AC4" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AD4" s="7"/>
       <c r="AE4" s="10" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AF4" s="10"/>
       <c r="AG4" s="7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AH4" s="7"/>
       <c r="AI4" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AJ4" s="7"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5">
       <c r="B5" s="3">
         <v>10014</v>
       </c>
@@ -2352,106 +2356,106 @@
         <v>1003</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1010</v>
+        <v>42</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H5" s="5">
         <v>21600</v>
       </c>
-      <c r="I5" s="3">
-        <v>1011</v>
+      <c r="I5" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J5" s="5">
         <v>26800</v>
       </c>
-      <c r="K5" s="2">
-        <v>1012</v>
+      <c r="K5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L5" s="5">
         <v>-58702</v>
       </c>
-      <c r="M5" s="2">
-        <v>1014</v>
+      <c r="M5" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N5" s="3">
         <v>0</v>
       </c>
-      <c r="O5" s="2">
-        <v>10001</v>
+      <c r="O5" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P5" s="5">
         <v>2000</v>
       </c>
-      <c r="Q5" s="3">
-        <v>10051</v>
+      <c r="Q5" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R5" s="5">
         <v>500</v>
       </c>
-      <c r="S5" s="2">
-        <v>10061</v>
+      <c r="S5" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T5" s="5">
         <v>10000</v>
       </c>
-      <c r="U5" s="3">
-        <v>10071</v>
+      <c r="U5" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V5" s="5">
         <v>500</v>
       </c>
-      <c r="W5" s="3">
-        <v>10081</v>
+      <c r="W5" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X5" s="5">
         <v>30000</v>
       </c>
-      <c r="Y5" s="3">
-        <v>1009</v>
+      <c r="Y5" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z5" s="3">
         <v>300001</v>
       </c>
-      <c r="AA5" s="3">
-        <v>10021</v>
+      <c r="AA5" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB5" s="5">
         <v>100</v>
       </c>
-      <c r="AC5" s="3">
-        <v>1001</v>
+      <c r="AC5" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD5" s="5">
         <v>100</v>
       </c>
-      <c r="AE5" s="3">
-        <v>10041</v>
+      <c r="AE5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF5" s="5">
         <v>100</v>
       </c>
-      <c r="AG5" s="3">
-        <v>1003</v>
+      <c r="AG5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH5" s="5">
         <v>100</v>
       </c>
-      <c r="AI5" s="3">
-        <v>1015</v>
+      <c r="AI5" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6">
       <c r="B6" s="3">
         <v>10015</v>
       </c>
@@ -2459,106 +2463,106 @@
         <v>1003</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1010</v>
+        <v>42</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H6" s="5">
         <v>56000</v>
       </c>
-      <c r="I6" s="3">
-        <v>1011</v>
+      <c r="I6" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J6" s="5">
         <v>25180</v>
       </c>
-      <c r="K6" s="2">
-        <v>1012</v>
+      <c r="K6" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L6" s="5">
         <v>-23633</v>
       </c>
-      <c r="M6" s="2">
-        <v>1014</v>
+      <c r="M6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N6" s="3">
         <v>0</v>
       </c>
-      <c r="O6" s="2">
-        <v>10001</v>
+      <c r="O6" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P6" s="5">
         <v>2000</v>
       </c>
-      <c r="Q6" s="3">
-        <v>10051</v>
+      <c r="Q6" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R6" s="5">
         <v>500</v>
       </c>
-      <c r="S6" s="2">
-        <v>10061</v>
+      <c r="S6" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T6" s="5">
         <v>10000</v>
       </c>
-      <c r="U6" s="3">
-        <v>10071</v>
+      <c r="U6" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V6" s="5">
         <v>500</v>
       </c>
-      <c r="W6" s="3">
-        <v>10081</v>
+      <c r="W6" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X6" s="5">
         <v>30000</v>
       </c>
-      <c r="Y6" s="3">
-        <v>1009</v>
+      <c r="Y6" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z6" s="3">
         <v>300001</v>
       </c>
-      <c r="AA6" s="3">
-        <v>10021</v>
+      <c r="AA6" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB6" s="5">
         <v>100</v>
       </c>
-      <c r="AC6" s="3">
-        <v>1001</v>
+      <c r="AC6" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD6" s="5">
         <v>100</v>
       </c>
-      <c r="AE6" s="3">
-        <v>10041</v>
+      <c r="AE6" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF6" s="5">
         <v>100</v>
       </c>
-      <c r="AG6" s="3">
-        <v>1003</v>
+      <c r="AG6" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH6" s="5">
         <v>100</v>
       </c>
-      <c r="AI6" s="3">
-        <v>1015</v>
+      <c r="AI6" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ6" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7">
       <c r="B7" s="3">
         <v>10016</v>
       </c>
@@ -2566,106 +2570,106 @@
         <v>1003</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1010</v>
+        <v>42</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H7" s="5">
         <v>36310</v>
       </c>
-      <c r="I7" s="3">
-        <v>1011</v>
+      <c r="I7" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J7" s="5">
         <v>25180</v>
       </c>
-      <c r="K7" s="2">
-        <v>1012</v>
+      <c r="K7" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L7" s="5">
         <v>-23634</v>
       </c>
-      <c r="M7" s="2">
-        <v>1014</v>
+      <c r="M7" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N7" s="3">
         <v>0</v>
       </c>
-      <c r="O7" s="2">
-        <v>10001</v>
+      <c r="O7" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P7" s="5">
         <v>2000</v>
       </c>
-      <c r="Q7" s="3">
-        <v>10051</v>
+      <c r="Q7" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R7" s="5">
         <v>500</v>
       </c>
-      <c r="S7" s="2">
-        <v>10061</v>
+      <c r="S7" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T7" s="5">
         <v>10000</v>
       </c>
-      <c r="U7" s="3">
-        <v>10071</v>
+      <c r="U7" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V7" s="5">
         <v>500</v>
       </c>
-      <c r="W7" s="3">
-        <v>10081</v>
+      <c r="W7" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X7" s="5">
         <v>30000</v>
       </c>
-      <c r="Y7" s="3">
-        <v>1009</v>
+      <c r="Y7" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z7" s="3">
         <v>300001</v>
       </c>
-      <c r="AA7" s="3">
-        <v>10021</v>
+      <c r="AA7" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB7" s="5">
         <v>100</v>
       </c>
-      <c r="AC7" s="3">
-        <v>1001</v>
+      <c r="AC7" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD7" s="5">
         <v>100</v>
       </c>
-      <c r="AE7" s="3">
-        <v>10041</v>
+      <c r="AE7" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF7" s="5">
         <v>100</v>
       </c>
-      <c r="AG7" s="3">
-        <v>1003</v>
+      <c r="AG7" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH7" s="5">
         <v>100</v>
       </c>
-      <c r="AI7" s="3">
-        <v>1015</v>
+      <c r="AI7" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ7" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8">
       <c r="B8" s="3">
         <v>10017</v>
       </c>
@@ -2673,106 +2677,106 @@
         <v>1003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1010</v>
+        <v>42</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H8" s="5">
         <v>67170</v>
       </c>
-      <c r="I8" s="3">
-        <v>1011</v>
+      <c r="I8" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J8" s="5">
         <v>25180</v>
       </c>
-      <c r="K8" s="2">
-        <v>1012</v>
+      <c r="K8" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L8" s="5">
         <v>-40495</v>
       </c>
-      <c r="M8" s="2">
-        <v>1014</v>
+      <c r="M8" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
-      <c r="O8" s="2">
-        <v>10001</v>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P8" s="5">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
-        <v>10051</v>
+      <c r="Q8" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R8" s="5">
         <v>500</v>
       </c>
-      <c r="S8" s="2">
-        <v>10061</v>
+      <c r="S8" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T8" s="5">
         <v>10000</v>
       </c>
-      <c r="U8" s="3">
-        <v>10071</v>
+      <c r="U8" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V8" s="5">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
-        <v>10081</v>
+      <c r="W8" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X8" s="5">
         <v>30000</v>
       </c>
-      <c r="Y8" s="3">
-        <v>1009</v>
+      <c r="Y8" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z8" s="3">
         <v>300001</v>
       </c>
-      <c r="AA8" s="3">
-        <v>10021</v>
+      <c r="AA8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB8" s="5">
         <v>100</v>
       </c>
-      <c r="AC8" s="3">
-        <v>1001</v>
+      <c r="AC8" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD8" s="5">
         <v>100</v>
       </c>
-      <c r="AE8" s="3">
-        <v>10041</v>
+      <c r="AE8" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF8" s="5">
         <v>100</v>
       </c>
-      <c r="AG8" s="3">
-        <v>1003</v>
+      <c r="AG8" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH8" s="5">
         <v>100</v>
       </c>
-      <c r="AI8" s="3">
-        <v>1015</v>
+      <c r="AI8" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ8" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9">
       <c r="B9" s="3">
         <v>10018</v>
       </c>
@@ -2780,106 +2784,106 @@
         <v>1003</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1010</v>
+        <v>42</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H9" s="5">
         <v>59600</v>
       </c>
-      <c r="I9" s="3">
-        <v>1011</v>
+      <c r="I9" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J9" s="5">
         <v>25800</v>
       </c>
-      <c r="K9" s="2">
-        <v>1012</v>
+      <c r="K9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L9" s="5">
         <v>-87866</v>
       </c>
-      <c r="M9" s="2">
-        <v>1014</v>
+      <c r="M9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="2">
-        <v>10001</v>
+      <c r="O9" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P9" s="5">
         <v>2000</v>
       </c>
-      <c r="Q9" s="3">
-        <v>10051</v>
+      <c r="Q9" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R9" s="5">
         <v>500</v>
       </c>
-      <c r="S9" s="2">
-        <v>10061</v>
+      <c r="S9" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T9" s="5">
         <v>10000</v>
       </c>
-      <c r="U9" s="3">
-        <v>10071</v>
+      <c r="U9" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V9" s="5">
         <v>500</v>
       </c>
-      <c r="W9" s="3">
-        <v>10081</v>
+      <c r="W9" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X9" s="5">
         <v>30000</v>
       </c>
-      <c r="Y9" s="3">
-        <v>1009</v>
+      <c r="Y9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z9" s="3">
         <v>300001</v>
       </c>
-      <c r="AA9" s="3">
-        <v>10021</v>
+      <c r="AA9" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB9" s="5">
         <v>100</v>
       </c>
-      <c r="AC9" s="3">
-        <v>1001</v>
+      <c r="AC9" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD9" s="5">
         <v>100</v>
       </c>
-      <c r="AE9" s="3">
-        <v>10041</v>
+      <c r="AE9" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF9" s="5">
         <v>100</v>
       </c>
-      <c r="AG9" s="3">
-        <v>1003</v>
+      <c r="AG9" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH9" s="5">
         <v>100</v>
       </c>
-      <c r="AI9" s="3">
-        <v>1015</v>
+      <c r="AI9" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ9" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10">
       <c r="B10" s="3">
         <v>10019</v>
       </c>
@@ -2887,106 +2891,106 @@
         <v>1004</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1010</v>
+        <v>44</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H10" s="5">
         <v>58740</v>
       </c>
-      <c r="I10" s="3">
-        <v>1011</v>
+      <c r="I10" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J10" s="5">
         <v>28100</v>
       </c>
-      <c r="K10" s="2">
-        <v>1012</v>
+      <c r="K10" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L10" s="5">
         <v>-141407</v>
       </c>
-      <c r="M10" s="2">
-        <v>1014</v>
+      <c r="M10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="2">
-        <v>10001</v>
+      <c r="O10" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P10" s="5">
         <v>2000</v>
       </c>
-      <c r="Q10" s="3">
-        <v>10051</v>
+      <c r="Q10" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R10" s="5">
         <v>2000</v>
       </c>
-      <c r="S10" s="2">
-        <v>10061</v>
+      <c r="S10" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T10" s="5">
         <v>10000</v>
       </c>
-      <c r="U10" s="3">
-        <v>10071</v>
+      <c r="U10" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V10" s="5">
         <v>500</v>
       </c>
-      <c r="W10" s="3">
-        <v>10081</v>
+      <c r="W10" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X10" s="5">
         <v>30000</v>
       </c>
-      <c r="Y10" s="3">
-        <v>1009</v>
+      <c r="Y10" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z10" s="3">
         <v>300001</v>
       </c>
-      <c r="AA10" s="3">
-        <v>10021</v>
+      <c r="AA10" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB10" s="5">
         <v>100</v>
       </c>
-      <c r="AC10" s="3">
-        <v>1001</v>
+      <c r="AC10" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD10" s="5">
         <v>100</v>
       </c>
-      <c r="AE10" s="3">
-        <v>10041</v>
+      <c r="AE10" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF10" s="5">
         <v>100</v>
       </c>
-      <c r="AG10" s="3">
-        <v>1003</v>
+      <c r="AG10" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH10" s="5">
         <v>100</v>
       </c>
-      <c r="AI10" s="3">
-        <v>1015</v>
+      <c r="AI10" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ10" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11">
       <c r="B11" s="3">
         <v>10020</v>
       </c>
@@ -2994,106 +2998,106 @@
         <v>1004</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1010</v>
+        <v>44</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H11" s="5">
         <v>58740</v>
       </c>
-      <c r="I11" s="3">
-        <v>1011</v>
+      <c r="I11" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J11" s="5">
         <v>28100</v>
       </c>
-      <c r="K11" s="2">
-        <v>1012</v>
+      <c r="K11" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L11" s="5">
         <v>-130408</v>
       </c>
-      <c r="M11" s="2">
-        <v>1014</v>
+      <c r="M11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N11" s="3">
         <v>0</v>
       </c>
-      <c r="O11" s="2">
-        <v>10001</v>
+      <c r="O11" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P11" s="5">
         <v>2000</v>
       </c>
-      <c r="Q11" s="3">
-        <v>10051</v>
+      <c r="Q11" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R11" s="5">
         <v>2000</v>
       </c>
-      <c r="S11" s="2">
-        <v>10061</v>
+      <c r="S11" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T11" s="5">
         <v>10000</v>
       </c>
-      <c r="U11" s="3">
-        <v>10071</v>
+      <c r="U11" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V11" s="5">
         <v>500</v>
       </c>
-      <c r="W11" s="3">
-        <v>10081</v>
+      <c r="W11" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X11" s="5">
         <v>30000</v>
       </c>
-      <c r="Y11" s="3">
-        <v>1009</v>
+      <c r="Y11" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z11" s="3">
         <v>300001</v>
       </c>
-      <c r="AA11" s="3">
-        <v>10021</v>
+      <c r="AA11" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB11" s="5">
         <v>100</v>
       </c>
-      <c r="AC11" s="3">
-        <v>1001</v>
+      <c r="AC11" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD11" s="5">
         <v>100</v>
       </c>
-      <c r="AE11" s="3">
-        <v>10041</v>
+      <c r="AE11" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF11" s="5">
         <v>100</v>
       </c>
-      <c r="AG11" s="3">
-        <v>1003</v>
+      <c r="AG11" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH11" s="5">
         <v>100</v>
       </c>
-      <c r="AI11" s="3">
-        <v>1015</v>
+      <c r="AI11" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ11" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12">
       <c r="B12" s="3">
         <v>10021</v>
       </c>
@@ -3101,106 +3105,106 @@
         <v>1004</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1010</v>
+        <v>44</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H12" s="5">
         <v>67480</v>
       </c>
-      <c r="I12" s="3">
-        <v>1011</v>
+      <c r="I12" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J12" s="5">
         <v>28850</v>
       </c>
-      <c r="K12" s="2">
-        <v>1012</v>
+      <c r="K12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L12" s="5">
         <v>-130409</v>
       </c>
-      <c r="M12" s="2">
-        <v>1014</v>
+      <c r="M12" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N12" s="3">
         <v>0</v>
       </c>
-      <c r="O12" s="2">
-        <v>10001</v>
+      <c r="O12" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P12" s="5">
         <v>2000</v>
       </c>
-      <c r="Q12" s="3">
-        <v>10051</v>
+      <c r="Q12" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R12" s="5">
         <v>2000</v>
       </c>
-      <c r="S12" s="2">
-        <v>10061</v>
+      <c r="S12" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T12" s="5">
         <v>10000</v>
       </c>
-      <c r="U12" s="3">
-        <v>10071</v>
+      <c r="U12" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V12" s="5">
         <v>500</v>
       </c>
-      <c r="W12" s="3">
-        <v>10081</v>
+      <c r="W12" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X12" s="5">
         <v>30000</v>
       </c>
-      <c r="Y12" s="3">
-        <v>1009</v>
+      <c r="Y12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z12" s="3">
         <v>300001</v>
       </c>
-      <c r="AA12" s="3">
-        <v>10021</v>
+      <c r="AA12" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB12" s="5">
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
-        <v>1001</v>
+      <c r="AC12" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD12" s="5">
         <v>100</v>
       </c>
-      <c r="AE12" s="3">
-        <v>10041</v>
+      <c r="AE12" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF12" s="5">
         <v>100</v>
       </c>
-      <c r="AG12" s="3">
-        <v>1003</v>
+      <c r="AG12" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH12" s="5">
         <v>100</v>
       </c>
-      <c r="AI12" s="3">
-        <v>1015</v>
+      <c r="AI12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ12" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13">
       <c r="B13" s="3">
         <v>10022</v>
       </c>
@@ -3208,106 +3212,106 @@
         <v>1004</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1010</v>
+        <v>44</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H13" s="5">
         <v>67480</v>
       </c>
-      <c r="I13" s="3">
-        <v>1011</v>
+      <c r="I13" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J13" s="5">
         <v>27510</v>
       </c>
-      <c r="K13" s="2">
-        <v>1012</v>
+      <c r="K13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L13" s="5">
         <v>-34791</v>
       </c>
-      <c r="M13" s="2">
-        <v>1014</v>
+      <c r="M13" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="2">
-        <v>10001</v>
+      <c r="O13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P13" s="5">
         <v>2000</v>
       </c>
-      <c r="Q13" s="3">
-        <v>10051</v>
+      <c r="Q13" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R13" s="5">
         <v>2000</v>
       </c>
-      <c r="S13" s="2">
-        <v>10061</v>
+      <c r="S13" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T13" s="5">
         <v>10000</v>
       </c>
-      <c r="U13" s="3">
-        <v>10071</v>
+      <c r="U13" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V13" s="5">
         <v>500</v>
       </c>
-      <c r="W13" s="3">
-        <v>10081</v>
+      <c r="W13" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X13" s="5">
         <v>30000</v>
       </c>
-      <c r="Y13" s="3">
-        <v>1009</v>
+      <c r="Y13" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z13" s="3">
         <v>300001</v>
       </c>
-      <c r="AA13" s="3">
-        <v>10021</v>
+      <c r="AA13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB13" s="5">
         <v>100</v>
       </c>
-      <c r="AC13" s="3">
-        <v>1001</v>
+      <c r="AC13" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD13" s="5">
         <v>100</v>
       </c>
-      <c r="AE13" s="3">
-        <v>10041</v>
+      <c r="AE13" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF13" s="5">
         <v>100</v>
       </c>
-      <c r="AG13" s="3">
-        <v>1003</v>
+      <c r="AG13" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH13" s="5">
         <v>100</v>
       </c>
-      <c r="AI13" s="3">
-        <v>1015</v>
+      <c r="AI13" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ13" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14">
       <c r="B14" s="3">
         <v>10023</v>
       </c>
@@ -3315,106 +3319,106 @@
         <v>1004</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1010</v>
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H14" s="5">
         <v>67480</v>
       </c>
-      <c r="I14" s="3">
-        <v>1011</v>
+      <c r="I14" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J14" s="5">
         <v>25900</v>
       </c>
-      <c r="K14" s="2">
-        <v>1012</v>
+      <c r="K14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L14" s="5">
         <v>-93811</v>
       </c>
-      <c r="M14" s="2">
-        <v>1014</v>
+      <c r="M14" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="2">
-        <v>10001</v>
+      <c r="O14" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P14" s="5">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>10051</v>
+      <c r="Q14" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R14" s="5">
         <v>2000</v>
       </c>
-      <c r="S14" s="2">
-        <v>10061</v>
+      <c r="S14" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T14" s="5">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
-        <v>10071</v>
+      <c r="U14" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V14" s="5">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
-        <v>10081</v>
+      <c r="W14" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X14" s="5">
         <v>30000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>1009</v>
+      <c r="Y14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z14" s="3">
         <v>300001</v>
       </c>
-      <c r="AA14" s="3">
-        <v>10021</v>
+      <c r="AA14" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB14" s="5">
         <v>100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>1001</v>
+      <c r="AC14" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD14" s="5">
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>10041</v>
+      <c r="AE14" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF14" s="5">
         <v>100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>1003</v>
+      <c r="AG14" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH14" s="5">
         <v>100</v>
       </c>
-      <c r="AI14" s="3">
-        <v>1015</v>
+      <c r="AI14" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ14" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15">
       <c r="B15" s="3">
         <v>10024</v>
       </c>
@@ -3422,106 +3426,106 @@
         <v>1005</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1010</v>
+        <v>47</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H15" s="3">
         <v>10000</v>
       </c>
-      <c r="I15" s="3">
-        <v>1011</v>
+      <c r="I15" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J15" s="3">
         <v>25200</v>
       </c>
-      <c r="K15" s="2">
-        <v>1012</v>
+      <c r="K15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="2">
-        <v>1014</v>
+      <c r="M15" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="2">
-        <v>10001</v>
+      <c r="O15" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P15" s="5">
         <v>2000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>10051</v>
+      <c r="Q15" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R15" s="5">
         <v>2000</v>
       </c>
-      <c r="S15" s="2">
-        <v>10061</v>
+      <c r="S15" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T15" s="5">
         <v>10000</v>
       </c>
-      <c r="U15" s="3">
-        <v>10071</v>
+      <c r="U15" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V15" s="5">
         <v>500</v>
       </c>
-      <c r="W15" s="3">
-        <v>10081</v>
+      <c r="W15" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X15" s="5">
         <v>30000</v>
       </c>
-      <c r="Y15" s="3">
-        <v>1009</v>
+      <c r="Y15" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3">
-        <v>10021</v>
+      <c r="AA15" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB15" s="5">
         <v>100</v>
       </c>
-      <c r="AC15" s="3">
-        <v>1001</v>
+      <c r="AC15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD15" s="5">
         <v>100</v>
       </c>
-      <c r="AE15" s="3">
-        <v>10041</v>
+      <c r="AE15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF15" s="5">
         <v>100</v>
       </c>
-      <c r="AG15" s="3">
-        <v>1003</v>
+      <c r="AG15" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH15" s="5">
         <v>100</v>
       </c>
-      <c r="AI15" s="3">
-        <v>1015</v>
+      <c r="AI15" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ15" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16">
       <c r="B16" s="3">
         <v>10025</v>
       </c>
@@ -3529,106 +3533,106 @@
         <v>1005</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="3">
-        <v>1010</v>
+        <v>48</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H16" s="3">
         <v>-10000</v>
       </c>
-      <c r="I16" s="3">
-        <v>1011</v>
+      <c r="I16" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J16" s="3">
         <v>25200</v>
       </c>
-      <c r="K16" s="2">
-        <v>1012</v>
+      <c r="K16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L16" s="3">
         <v>0</v>
       </c>
-      <c r="M16" s="2">
-        <v>1014</v>
+      <c r="M16" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N16" s="3">
         <v>0</v>
       </c>
-      <c r="O16" s="2">
-        <v>10001</v>
+      <c r="O16" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P16" s="5">
         <v>2000</v>
       </c>
-      <c r="Q16" s="3">
-        <v>10051</v>
+      <c r="Q16" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R16" s="5">
         <v>2000</v>
       </c>
-      <c r="S16" s="2">
-        <v>10061</v>
+      <c r="S16" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T16" s="5">
         <v>10000</v>
       </c>
-      <c r="U16" s="3">
-        <v>10071</v>
+      <c r="U16" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V16" s="5">
         <v>500</v>
       </c>
-      <c r="W16" s="3">
-        <v>10081</v>
+      <c r="W16" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X16" s="5">
         <v>30000</v>
       </c>
-      <c r="Y16" s="3">
-        <v>1009</v>
+      <c r="Y16" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z16" s="3">
         <v>0</v>
       </c>
-      <c r="AA16" s="3">
-        <v>10021</v>
+      <c r="AA16" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB16" s="5">
         <v>100</v>
       </c>
-      <c r="AC16" s="3">
-        <v>1001</v>
+      <c r="AC16" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD16" s="5">
         <v>100</v>
       </c>
-      <c r="AE16" s="3">
-        <v>10041</v>
+      <c r="AE16" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF16" s="5">
         <v>100</v>
       </c>
-      <c r="AG16" s="3">
-        <v>1003</v>
+      <c r="AG16" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH16" s="5">
         <v>100</v>
       </c>
-      <c r="AI16" s="3">
-        <v>1015</v>
+      <c r="AI16" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ16" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:36">
+    <row r="17">
       <c r="B17" s="3">
         <v>10026</v>
       </c>
@@ -3636,106 +3640,106 @@
         <v>1002</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1010</v>
+        <v>32</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H17" s="3">
         <v>0</v>
       </c>
-      <c r="I17" s="3">
-        <v>1011</v>
+      <c r="I17" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="J17" s="3">
         <v>25200</v>
       </c>
-      <c r="K17" s="2">
-        <v>1012</v>
+      <c r="K17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" s="2">
-        <v>1014</v>
+      <c r="M17" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N17" s="3">
         <v>270</v>
       </c>
-      <c r="O17" s="2">
-        <v>10001</v>
+      <c r="O17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P17" s="5">
         <v>0</v>
       </c>
-      <c r="Q17" s="3">
-        <v>10051</v>
+      <c r="Q17" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="R17" s="5">
         <v>500</v>
       </c>
-      <c r="S17" s="2">
-        <v>10061</v>
+      <c r="S17" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="T17" s="5">
         <v>0</v>
       </c>
-      <c r="U17" s="3">
-        <v>10071</v>
+      <c r="U17" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="V17" s="5">
         <v>500</v>
       </c>
-      <c r="W17" s="3">
-        <v>10081</v>
+      <c r="W17" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="X17" s="5">
         <v>30000</v>
       </c>
-      <c r="Y17" s="3">
-        <v>1009</v>
+      <c r="Y17" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z17" s="3">
         <v>200131</v>
       </c>
-      <c r="AA17" s="3">
-        <v>10021</v>
+      <c r="AA17" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="AB17" s="5">
         <v>100</v>
       </c>
-      <c r="AC17" s="3">
-        <v>1001</v>
+      <c r="AC17" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD17" s="5">
         <v>100</v>
       </c>
-      <c r="AE17" s="3">
-        <v>10041</v>
+      <c r="AE17" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AF17" s="5">
         <v>100</v>
       </c>
-      <c r="AG17" s="3">
-        <v>1003</v>
+      <c r="AG17" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="AH17" s="5">
         <v>100</v>
       </c>
-      <c r="AI17" s="3">
-        <v>1015</v>
+      <c r="AI17" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AJ17" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:36">
+    <row r="18">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -3773,7 +3777,7 @@
       <c r="AJ18" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="G1:AJ1"/>
     <mergeCell ref="G2:AJ2"/>
@@ -3796,5 +3800,11 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>